--- a/data/trans_orig/P2A_lim_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95331</t>
+          <t>96031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134502</t>
+          <t>134185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135666</t>
+          <t>136110</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>182490</t>
+          <t>183498</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242482</t>
+          <t>243953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303709</t>
+          <t>305503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>893654</t>
+          <t>893971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>932825</t>
+          <t>932125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1131395</t>
+          <t>1130387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1178219</t>
+          <t>1177775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2038332</t>
+          <t>2036538</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2099559</t>
+          <t>2098088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>66078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100633</t>
+          <t>101863</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69095</t>
+          <t>66812</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103669</t>
+          <t>103025</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141495</t>
+          <t>143134</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192394</t>
+          <t>196116</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1589088</t>
+          <t>1587858</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1624400</t>
+          <t>1623643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1480956</t>
+          <t>1481600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1515530</t>
+          <t>1517813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3081952</t>
+          <t>3078230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3132851</t>
+          <t>3131212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62554</t>
+          <t>62334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517109</t>
+          <t>517607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537478</t>
+          <t>537858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>436766</t>
+          <t>437605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458368</t>
+          <t>458148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>963246</t>
+          <t>963466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>991258</t>
+          <t>991162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189845</t>
+          <t>189776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247810</t>
+          <t>248188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241531</t>
+          <t>239778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307359</t>
+          <t>302984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448730</t>
+          <t>449897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>532442</t>
+          <t>534914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3019456</t>
+          <t>3019078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3077421</t>
+          <t>3077490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3067562</t>
+          <t>3071937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3133390</t>
+          <t>3135143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6109745</t>
+          <t>6107273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6193457</t>
+          <t>6192290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134393</t>
+          <t>131944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183368</t>
+          <t>180347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185251</t>
+          <t>185292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241580</t>
+          <t>244352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>331760</t>
+          <t>331914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>406573</t>
+          <t>406099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>790289</t>
+          <t>793310</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>839264</t>
+          <t>841713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1096217</t>
+          <t>1093445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1152546</t>
+          <t>1152505</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1904881</t>
+          <t>1905355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1979694</t>
+          <t>1979540</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123091</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170195</t>
+          <t>169862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136142</t>
+          <t>138032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186236</t>
+          <t>188265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273660</t>
+          <t>273284</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>346197</t>
+          <t>342536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1791582</t>
+          <t>1791915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1838686</t>
+          <t>1843286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1569672</t>
+          <t>1567643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1619766</t>
+          <t>1617876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3371488</t>
+          <t>3375149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3444025</t>
+          <t>3444401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36727</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52293</t>
+          <t>51766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45240</t>
+          <t>46361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79365</t>
+          <t>78166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444454</t>
+          <t>443108</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465800</t>
+          <t>465396</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406338</t>
+          <t>406865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432408</t>
+          <t>434035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>860448</t>
+          <t>861647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>894573</t>
+          <t>893452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291233</t>
+          <t>287559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>366162</t>
+          <t>365751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>369456</t>
+          <t>372773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>447942</t>
+          <t>451948</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>682573</t>
+          <t>686539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>782000</t>
+          <t>794704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3050453</t>
+          <t>3050864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3125382</t>
+          <t>3129056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3104394</t>
+          <t>3100388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3182880</t>
+          <t>3179563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6186951</t>
+          <t>6174247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6286378</t>
+          <t>6282412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64612</t>
+          <t>66793</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99772</t>
+          <t>102862</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131310</t>
+          <t>132616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179619</t>
+          <t>179231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207501</t>
+          <t>208590</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265978</t>
+          <t>267546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>653491</t>
+          <t>650401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688651</t>
+          <t>686470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>811911</t>
+          <t>812299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>860220</t>
+          <t>858914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1478815</t>
+          <t>1477247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1537292</t>
+          <t>1536203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107620</t>
+          <t>108297</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155465</t>
+          <t>155559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105212</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150536</t>
+          <t>150566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>226586</t>
+          <t>226749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292438</t>
+          <t>293353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909609</t>
+          <t>1909515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1957454</t>
+          <t>1956777</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1834775</t>
+          <t>1834745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1880099</t>
+          <t>1879226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3757947</t>
+          <t>3757032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3823799</t>
+          <t>3823636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>33381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64765</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508705</t>
+          <t>509173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528579</t>
+          <t>527871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>510997</t>
+          <t>509467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530446</t>
+          <t>530910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1026002</t>
+          <t>1026653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1054032</t>
+          <t>1055205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209437</t>
+          <t>205075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269643</t>
+          <t>269529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>275902</t>
+          <t>274749</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>345574</t>
+          <t>341924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>499506</t>
+          <t>498412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>592157</t>
+          <t>593264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3091248</t>
+          <t>3091362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3151454</t>
+          <t>3155816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3179480</t>
+          <t>3183130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3249152</t>
+          <t>3250305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6293788</t>
+          <t>6292681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6386439</t>
+          <t>6387533</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023</t>
+          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114063</t>
+          <t>114241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150192</t>
+          <t>150737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184652</t>
+          <t>184682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219355</t>
+          <t>220744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306138</t>
+          <t>312057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>357663</t>
+          <t>358684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363346</t>
+          <t>362801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399475</t>
+          <t>399297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>536153</t>
+          <t>534764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>570856</t>
+          <t>570826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>911383</t>
+          <t>910362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>962908</t>
+          <t>956989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177838</t>
+          <t>181957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>299158</t>
+          <t>297906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>238073</t>
+          <t>240673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>945946</t>
+          <t>991022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>476951</t>
+          <t>473912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1326315</t>
+          <t>1254689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1976731</t>
+          <t>1977983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2098051</t>
+          <t>2093932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1281032</t>
+          <t>1235956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1988905</t>
+          <t>1986305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3176553</t>
+          <t>3248179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4025917</t>
+          <t>4028956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44386</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>76039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41103</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65060</t>
+          <t>63723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91973</t>
+          <t>90481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131844</t>
+          <t>130059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>560558</t>
+          <t>563698</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595351</t>
+          <t>596196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>589655</t>
+          <t>590992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>613612</t>
+          <t>614969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1162608</t>
+          <t>1164393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1202479</t>
+          <t>1203971</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>341532</t>
+          <t>338553</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>495614</t>
+          <t>492754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>492729</t>
+          <t>500137</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1135461</t>
+          <t>1251266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>918937</t>
+          <t>921166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1664310</t>
+          <t>1732337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2933551</t>
+          <t>2936411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3087633</t>
+          <t>3090612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2501740</t>
+          <t>2385935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3144472</t>
+          <t>3137064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5402056</t>
+          <t>5334029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6147429</t>
+          <t>6145200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_lim_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96031</t>
+          <t>93925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134185</t>
+          <t>133969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136110</t>
+          <t>138134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183498</t>
+          <t>183604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243953</t>
+          <t>243681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305503</t>
+          <t>307192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>893971</t>
+          <t>894187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>932125</t>
+          <t>934231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1130387</t>
+          <t>1130281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1177775</t>
+          <t>1175751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2036538</t>
+          <t>2034849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2098088</t>
+          <t>2098360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66078</t>
+          <t>67434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101863</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66812</t>
+          <t>66441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103025</t>
+          <t>103706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143134</t>
+          <t>143194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196116</t>
+          <t>196167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1587858</t>
+          <t>1587628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1623643</t>
+          <t>1622287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1481600</t>
+          <t>1480919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1517813</t>
+          <t>1518184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3078230</t>
+          <t>3078179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3131212</t>
+          <t>3131152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>32505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18264</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34638</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>64043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517607</t>
+          <t>516884</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>537858</t>
+          <t>537458</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437605</t>
+          <t>436147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458148</t>
+          <t>458078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>963466</t>
+          <t>961757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>991162</t>
+          <t>991391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189776</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248188</t>
+          <t>250372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239778</t>
+          <t>244338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>302984</t>
+          <t>305926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>449897</t>
+          <t>448197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534914</t>
+          <t>532244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3019078</t>
+          <t>3016894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3077490</t>
+          <t>3078028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3071937</t>
+          <t>3068995</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3135143</t>
+          <t>3130583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6107273</t>
+          <t>6109943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6192290</t>
+          <t>6193990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131944</t>
+          <t>135329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180347</t>
+          <t>184019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185292</t>
+          <t>186434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>244352</t>
+          <t>241483</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>331914</t>
+          <t>332003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>406099</t>
+          <t>406459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>793310</t>
+          <t>789638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>841713</t>
+          <t>838328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1093445</t>
+          <t>1096314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1152505</t>
+          <t>1151363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1905355</t>
+          <t>1904995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1979540</t>
+          <t>1979451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118491</t>
+          <t>119978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169862</t>
+          <t>169813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138032</t>
+          <t>137490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188265</t>
+          <t>187672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273284</t>
+          <t>268757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>342536</t>
+          <t>339514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1791915</t>
+          <t>1791964</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1843286</t>
+          <t>1841799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1567643</t>
+          <t>1568236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1617876</t>
+          <t>1618418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3375149</t>
+          <t>3378171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3444401</t>
+          <t>3448928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>36609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>25108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51766</t>
+          <t>50322</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>45607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78166</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443108</t>
+          <t>444572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>465396</t>
+          <t>465854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406865</t>
+          <t>408309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>434035</t>
+          <t>433523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>861647</t>
+          <t>861679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>893452</t>
+          <t>894206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>287559</t>
+          <t>290534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>365751</t>
+          <t>362734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>372773</t>
+          <t>364053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>451948</t>
+          <t>446458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>686539</t>
+          <t>681203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>794704</t>
+          <t>789471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3050864</t>
+          <t>3053881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3129056</t>
+          <t>3126081</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3100388</t>
+          <t>3105878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3179563</t>
+          <t>3188283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6174247</t>
+          <t>6179480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6282412</t>
+          <t>6287748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66793</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>101497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132616</t>
+          <t>129725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179231</t>
+          <t>180495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208590</t>
+          <t>207468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267546</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>650401</t>
+          <t>651766</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686470</t>
+          <t>684871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>812299</t>
+          <t>811035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>858914</t>
+          <t>861805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1477247</t>
+          <t>1478117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1536203</t>
+          <t>1537325</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108297</t>
+          <t>111170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>155559</t>
+          <t>157693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106085</t>
+          <t>106249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150566</t>
+          <t>151780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>226749</t>
+          <t>225994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>293353</t>
+          <t>293732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909515</t>
+          <t>1907381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1956777</t>
+          <t>1953904</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1834745</t>
+          <t>1833531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1879226</t>
+          <t>1879062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3757032</t>
+          <t>3756653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3823636</t>
+          <t>3824391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33381</t>
+          <t>34916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>65480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509173</t>
+          <t>507638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>527871</t>
+          <t>528436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509467</t>
+          <t>509504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530910</t>
+          <t>530669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1026653</t>
+          <t>1025287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1055205</t>
+          <t>1053267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205075</t>
+          <t>207356</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269529</t>
+          <t>271037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>274749</t>
+          <t>272177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>341924</t>
+          <t>342558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>498412</t>
+          <t>498444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>593264</t>
+          <t>588974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3091362</t>
+          <t>3089854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3155816</t>
+          <t>3153535</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3183130</t>
+          <t>3182496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3250305</t>
+          <t>3252877</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6292681</t>
+          <t>6296971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6387533</t>
+          <t>6387501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>130760</t>
+          <t>138891</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114241</t>
+          <t>121370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150737</t>
+          <t>159003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>202486</t>
+          <t>220996</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184682</t>
+          <t>203619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220744</t>
+          <t>242105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>333246</t>
+          <t>359887</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>312057</t>
+          <t>334675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>358684</t>
+          <t>387907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>382778</t>
+          <t>438172</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362801</t>
+          <t>418060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399297</t>
+          <t>455693</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>553022</t>
+          <t>601042</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>534764</t>
+          <t>579933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>570826</t>
+          <t>618419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>935800</t>
+          <t>1039214</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>910362</t>
+          <t>1011194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956989</t>
+          <t>1064426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513538</t>
+          <t>577063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513538</t>
+          <t>577063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513538</t>
+          <t>577063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269046</t>
+          <t>1399101</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269046</t>
+          <t>1399101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269046</t>
+          <t>1399101</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>252047</t>
+          <t>270846</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181957</t>
+          <t>240383</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>297906</t>
+          <t>304930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>431321</t>
+          <t>258928</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240673</t>
+          <t>233276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>991022</t>
+          <t>287130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>683368</t>
+          <t>529775</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>473912</t>
+          <t>492135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1254689</t>
+          <t>575273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2023842</t>
+          <t>1941504</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1977983</t>
+          <t>1907420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2093932</t>
+          <t>1971967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1795657</t>
+          <t>1900623</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1235956</t>
+          <t>1872421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1986305</t>
+          <t>1926275</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3819500</t>
+          <t>3842127</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3248179</t>
+          <t>3796629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4028956</t>
+          <t>3879767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2275889</t>
+          <t>2212350</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2275889</t>
+          <t>2212350</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2275889</t>
+          <t>2212350</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2226978</t>
+          <t>2159551</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2226978</t>
+          <t>2159551</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2226978</t>
+          <t>2159551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4502868</t>
+          <t>4371902</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4502868</t>
+          <t>4371902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4502868</t>
+          <t>4371902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>64105</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>49793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76039</t>
+          <t>83113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>57473</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>45660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63723</t>
+          <t>71223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109874</t>
+          <t>121578</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90481</t>
+          <t>101535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130059</t>
+          <t>147345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>581041</t>
+          <t>640294</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>563698</t>
+          <t>621286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>596196</t>
+          <t>654606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>603537</t>
+          <t>671281</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>590992</t>
+          <t>657531</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>614969</t>
+          <t>683094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1184578</t>
+          <t>1311576</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1164393</t>
+          <t>1285809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1203971</t>
+          <t>1331619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>639737</t>
+          <t>704399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>639737</t>
+          <t>704399</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>639737</t>
+          <t>704399</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>654715</t>
+          <t>728754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>654715</t>
+          <t>728754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>654715</t>
+          <t>728754</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1294452</t>
+          <t>1433154</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1294452</t>
+          <t>1433154</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1294452</t>
+          <t>1433154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>441503</t>
+          <t>473843</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>338553</t>
+          <t>432825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>492754</t>
+          <t>515766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>684985</t>
+          <t>537397</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>500137</t>
+          <t>502430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1251266</t>
+          <t>574197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1126488</t>
+          <t>1011240</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>921166</t>
+          <t>957950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1732337</t>
+          <t>1065769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2987662</t>
+          <t>3019970</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2936411</t>
+          <t>2978047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3090612</t>
+          <t>3060988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2952216</t>
+          <t>3172946</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2385935</t>
+          <t>3136146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3137064</t>
+          <t>3207913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5939878</t>
+          <t>6192916</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5334029</t>
+          <t>6138387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6145200</t>
+          <t>6246206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3429165</t>
+          <t>3493813</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3429165</t>
+          <t>3493813</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3429165</t>
+          <t>3493813</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3637201</t>
+          <t>3710343</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3637201</t>
+          <t>3710343</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3637201</t>
+          <t>3710343</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7066366</t>
+          <t>7204156</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7066366</t>
+          <t>7204156</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7066366</t>
+          <t>7204156</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_lim_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_lim_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2007 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2012 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
+          <t>Población según si convive con personas con alguna limitación (física, sensorial o psíquica) en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
